--- a/AAII_Financials/Yearly/MSFT_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/MSFT_YR_FIN.xlsx
@@ -656,219 +656,232 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:R102"/>
+  <dimension ref="A5:S102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="17" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="17" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="18" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:19" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E7" s="2">
         <v>45838</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45473</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45107</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44742</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44377</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44012</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>43646</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>43281</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>42916</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>42551</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>42185</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>41820</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>41455</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>41090</v>
       </c>
-      <c r="R7" s="2"/>
-    </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S7" s="2"/>
+    </row>
+    <row r="8" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>331839000</v>
+      </c>
+      <c r="E8" s="3">
         <v>281724000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>245122000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>211915000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>198270000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>168088000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>143015000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>125843000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>110360000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>96571000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>91154000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>93580000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>86833000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>77849000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>73723000</v>
       </c>
-      <c r="R8" s="3"/>
-    </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S8" s="3"/>
+    </row>
+    <row r="9" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>106374000</v>
+      </c>
+      <c r="E9" s="3">
         <v>87831000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>74114000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>65863000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>62650000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>52232000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>46078000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>42910000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>38353000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>34261000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>32780000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>33038000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>27078000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>20385000</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>17530000</v>
       </c>
-      <c r="R9" s="3"/>
-    </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S9" s="3"/>
+    </row>
+    <row r="10" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>225465000</v>
+      </c>
+      <c r="E10" s="3">
         <v>193893000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>171008000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>146052000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>135620000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>115856000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>96937000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>82933000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>72007000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>62310000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>58374000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>60542000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>59755000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>57464000</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>56193000</v>
       </c>
-      <c r="R10" s="3"/>
-    </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S10" s="3"/>
+    </row>
+    <row r="11" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -887,56 +900,60 @@
       <c r="P11" s="3"/>
       <c r="Q11" s="3"/>
       <c r="R11" s="3"/>
-    </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S11" s="3"/>
+    </row>
+    <row r="12" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
+        <v>35562000</v>
+      </c>
+      <c r="E12" s="3">
         <v>32488000</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>29510000</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>27195000</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>24512000</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>20716000</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>19269000</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>16876000</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>14726000</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>12292000</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>11988000</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>12046000</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>11381000</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>10411000</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>9811000</v>
       </c>
-      <c r="R12" s="3"/>
-    </row>
-    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S12" s="3"/>
+    </row>
+    <row r="13" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -982,87 +999,93 @@
       <c r="Q13" s="3">
         <v>0</v>
       </c>
-      <c r="R13" s="3"/>
-    </row>
-    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="R13" s="3">
+        <v>0</v>
+      </c>
+      <c r="S13" s="3"/>
+    </row>
+    <row r="14" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
       <c r="D14" s="3">
-        <v>5340000</v>
+        <v>-6249000</v>
       </c>
       <c r="E14" s="3">
-        <v>1614000</v>
+        <v>615000</v>
       </c>
       <c r="F14" s="3">
+        <v>295000</v>
+      </c>
+      <c r="G14" s="3">
         <v>383000</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>-474000</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>-1232000</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>-32000</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>-648000</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>-2479000</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>2400000</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>1432000</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>10194000</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>233000</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>208000</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>6193000</v>
       </c>
-      <c r="R14" s="3"/>
-    </row>
-    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S14" s="3"/>
+    </row>
+    <row r="15" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D15" s="3">
+        <v>39000000</v>
+      </c>
+      <c r="E15" s="3">
         <v>28000000</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>20000000</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>13500000</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>14600000</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>10900000</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>12300000</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>11600000</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>9900000</v>
       </c>
-      <c r="L15" s="3">
-        <v>0</v>
-      </c>
       <c r="M15" s="3">
         <v>0</v>
       </c>
@@ -1078,9 +1101,12 @@
       <c r="Q15" s="3">
         <v>0</v>
       </c>
-      <c r="R15" s="3"/>
-    </row>
-    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="R15" s="3">
+        <v>0</v>
+      </c>
+      <c r="S15" s="3"/>
+    </row>
+    <row r="16" spans="1:19" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1096,104 +1122,111 @@
       <c r="P16" s="3"/>
       <c r="Q16" s="3"/>
       <c r="R16" s="3"/>
-    </row>
-    <row r="17" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S16" s="3"/>
+    </row>
+    <row r="17" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D17" s="3">
+        <v>176602000</v>
+      </c>
+      <c r="E17" s="3">
         <v>153196000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>135689000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>123392000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>114887000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>98172000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>90056000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>82884000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>75302000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>67601000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>65398000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>75602000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>59180000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>51293000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>51960000</v>
       </c>
-      <c r="R17" s="3"/>
-    </row>
-    <row r="18" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S17" s="3"/>
+    </row>
+    <row r="18" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D18" s="3">
+        <v>155237000</v>
+      </c>
+      <c r="E18" s="3">
         <v>128528000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>109433000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>88523000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>83383000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>69916000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>52959000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>42959000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>35058000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>28970000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>25756000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>17978000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>27653000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>26556000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>21763000</v>
       </c>
-      <c r="R18" s="3"/>
-    </row>
-    <row r="19" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S18" s="3"/>
+    </row>
+    <row r="19" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>13</v>
       </c>
@@ -1212,248 +1245,264 @@
       <c r="P19" s="3"/>
       <c r="Q19" s="3"/>
       <c r="R19" s="3"/>
-    </row>
-    <row r="20" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S19" s="3"/>
+    </row>
+    <row r="20" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D20" s="3">
-        <v>-217000</v>
+        <v>-4228000</v>
       </c>
       <c r="E20" s="3">
-        <v>206000</v>
+        <v>4508000</v>
       </c>
       <c r="F20" s="3">
+        <v>1525000</v>
+      </c>
+      <c r="G20" s="3">
         <v>-172000</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>188000</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-153000</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>44000</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-5000</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>544000</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>5375000</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>2369000</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>1310000</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>764000</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>925000</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>884000</v>
       </c>
-      <c r="R20" s="3"/>
-    </row>
-    <row r="21" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S20" s="3"/>
+    </row>
+    <row r="21" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D21" s="3">
-        <v>156745000</v>
+        <v>198465000</v>
       </c>
       <c r="E21" s="3">
-        <v>129227000</v>
+        <v>152020000</v>
       </c>
       <c r="F21" s="3">
+        <v>127908000</v>
+      </c>
+      <c r="G21" s="3">
         <v>102195000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>97795000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>80969000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>65215000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>54564000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>44414000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>43123000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>34747000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>25245000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>33629000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>31236000</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>25614000</v>
       </c>
-      <c r="R21" s="3"/>
-    </row>
-    <row r="22" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S21" s="3"/>
+    </row>
+    <row r="22" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D22" s="3">
+        <v>3081000</v>
+      </c>
+      <c r="E22" s="3">
         <v>2425000</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>2983000</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>1995000</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>2047000</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>2330000</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>2591000</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>2686000</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>2733000</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>4444000</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>2486000</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>781000</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>597000</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>429000</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>380000</v>
       </c>
-      <c r="R22" s="3"/>
-    </row>
-    <row r="23" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S22" s="3"/>
+    </row>
+    <row r="23" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D23" s="3">
+        <v>165934000</v>
+      </c>
+      <c r="E23" s="3">
         <v>123627000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>107787000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>89311000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>83716000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>71102000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>53036000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>43688000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>36474000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>29901000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>25639000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>18507000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>27820000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>27052000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>22267000</v>
       </c>
-      <c r="R23" s="3"/>
-    </row>
-    <row r="24" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S23" s="3"/>
+    </row>
+    <row r="24" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D24" s="3">
+        <v>32185000</v>
+      </c>
+      <c r="E24" s="3">
         <v>21795000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>19651000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>16950000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>10978000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>9831000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>8755000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>4448000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>19903000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>4412000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>5100000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>6314000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>5746000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>5189000</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>5289000</v>
       </c>
-      <c r="R24" s="3"/>
-    </row>
-    <row r="25" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S24" s="3"/>
+    </row>
+    <row r="25" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>19</v>
       </c>
@@ -1499,105 +1548,114 @@
       <c r="Q25" s="3">
         <v>0</v>
       </c>
-      <c r="R25" s="3"/>
-    </row>
-    <row r="26" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R25" s="3">
+        <v>0</v>
+      </c>
+      <c r="S25" s="3"/>
+    </row>
+    <row r="26" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>20</v>
       </c>
       <c r="D26" s="3">
+        <v>133749000</v>
+      </c>
+      <c r="E26" s="3">
         <v>101832000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>88136000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>72361000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>72738000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>61271000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>44281000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>39240000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>16571000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>25489000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>20539000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>12193000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>22074000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>21863000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>16978000</v>
       </c>
-      <c r="R26" s="3"/>
-    </row>
-    <row r="27" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S26" s="3"/>
+    </row>
+    <row r="27" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D27" s="3">
+        <v>133749000</v>
+      </c>
+      <c r="E27" s="3">
         <v>101832000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>88136000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>72361000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>72738000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>61271000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>44281000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>39240000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>16571000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>25489000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>20539000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>12193000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>22074000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>21863000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>16978000</v>
       </c>
-      <c r="R27" s="3"/>
-    </row>
-    <row r="28" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S27" s="3"/>
+    </row>
+    <row r="28" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>22</v>
       </c>
@@ -1643,9 +1701,12 @@
       <c r="Q28" s="3">
         <v>0</v>
       </c>
-      <c r="R28" s="3"/>
-    </row>
-    <row r="29" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R28" s="3">
+        <v>0</v>
+      </c>
+      <c r="S28" s="3"/>
+    </row>
+    <row r="29" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>23</v>
       </c>
@@ -1673,8 +1734,8 @@
       <c r="K29" s="3">
         <v>0</v>
       </c>
-      <c r="L29" s="3" t="s">
-        <v>24</v>
+      <c r="L29" s="3">
+        <v>0</v>
       </c>
       <c r="M29" s="3" t="s">
         <v>24</v>
@@ -1691,9 +1752,12 @@
       <c r="Q29" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="R29" s="3"/>
-    </row>
-    <row r="30" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R29" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="S29" s="3"/>
+    </row>
+    <row r="30" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1739,9 +1803,12 @@
       <c r="Q30" s="3">
         <v>0</v>
       </c>
-      <c r="R30" s="3"/>
-    </row>
-    <row r="31" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R30" s="3">
+        <v>0</v>
+      </c>
+      <c r="S30" s="3"/>
+    </row>
+    <row r="31" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1787,105 +1854,114 @@
       <c r="Q31" s="3">
         <v>0</v>
       </c>
-      <c r="R31" s="3"/>
-    </row>
-    <row r="32" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R31" s="3">
+        <v>0</v>
+      </c>
+      <c r="S31" s="3"/>
+    </row>
+    <row r="32" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>217000</v>
+        <v>4228000</v>
       </c>
       <c r="E32" s="3">
-        <v>-206000</v>
+        <v>-4508000</v>
       </c>
       <c r="F32" s="3">
+        <v>-1525000</v>
+      </c>
+      <c r="G32" s="3">
         <v>172000</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-188000</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>153000</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-44000</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>5000</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-544000</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-5375000</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-2369000</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-1310000</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-764000</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-925000</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-884000</v>
       </c>
-      <c r="R32" s="3"/>
-    </row>
-    <row r="33" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S32" s="3"/>
+    </row>
+    <row r="33" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>133749000</v>
+      </c>
+      <c r="E33" s="3">
         <v>101832000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>88136000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>72361000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>72738000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>61271000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>44281000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>39240000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>16571000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>25489000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>20539000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>12193000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>22074000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>21863000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>16978000</v>
       </c>
-      <c r="R33" s="3"/>
-    </row>
-    <row r="34" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S33" s="3"/>
+    </row>
+    <row r="34" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1931,110 +2007,119 @@
       <c r="Q34" s="3">
         <v>0</v>
       </c>
-      <c r="R34" s="3"/>
-    </row>
-    <row r="35" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R34" s="3">
+        <v>0</v>
+      </c>
+      <c r="S34" s="3"/>
+    </row>
+    <row r="35" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>133749000</v>
+      </c>
+      <c r="E35" s="3">
         <v>101832000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>88136000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>72361000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>72738000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>61271000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>44281000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>39240000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>16571000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>25489000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>20539000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>12193000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>22074000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>21863000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>16978000</v>
       </c>
-      <c r="R35" s="3"/>
-    </row>
-    <row r="37" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S35" s="3"/>
+    </row>
+    <row r="37" spans="2:19" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E38" s="2">
         <v>45838</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45473</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45107</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44742</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44377</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44012</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>43646</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>43281</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>42916</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>42551</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>42185</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>41820</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>41455</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>41090</v>
       </c>
-      <c r="R38" s="2"/>
-    </row>
-    <row r="39" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S38" s="2"/>
+    </row>
+    <row r="39" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2053,8 +2138,9 @@
       <c r="P39" s="3"/>
       <c r="Q39" s="3"/>
       <c r="R39" s="3"/>
-    </row>
-    <row r="40" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S39" s="3"/>
+    </row>
+    <row r="40" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2073,440 +2159,468 @@
       <c r="P40" s="3"/>
       <c r="Q40" s="3"/>
       <c r="R40" s="3"/>
-    </row>
-    <row r="41" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S40" s="3"/>
+    </row>
+    <row r="41" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>20935000</v>
+      </c>
+      <c r="E41" s="3">
         <v>30242000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>18315000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>34704000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>13931000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>14224000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>13576000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>11356000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>11946000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>7663000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>6510000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>5595000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>8669000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>3804000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>6938000</v>
       </c>
-      <c r="R41" s="3"/>
-    </row>
-    <row r="42" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S41" s="3"/>
+    </row>
+    <row r="42" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>55908000</v>
+      </c>
+      <c r="E42" s="3">
         <v>64323000</v>
       </c>
-      <c r="E42" s="3">
-        <v>57228000</v>
-      </c>
       <c r="F42" s="3">
+        <v>57216000</v>
+      </c>
+      <c r="G42" s="3">
         <v>76552000</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>90818000</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>116032000</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>122916000</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>122476000</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>121718000</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>125218000</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>106657000</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>90687000</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>76796000</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>72971000</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>56102000</v>
       </c>
-      <c r="R42" s="3"/>
-    </row>
-    <row r="43" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S42" s="3"/>
+    </row>
+    <row r="43" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>108676000</v>
+      </c>
+      <c r="E43" s="3">
         <v>78105000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>67424000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>57888000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>50361000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>38043000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>32011000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>29524000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>26481000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>22431000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>18277000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>17908000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>19544000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>17486000</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>15780000</v>
       </c>
-      <c r="R43" s="3"/>
-    </row>
-    <row r="44" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S43" s="3"/>
+    </row>
+    <row r="44" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>1397000</v>
+      </c>
+      <c r="E44" s="3">
         <v>938000</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>1246000</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>2500000</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>3742000</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>2636000</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>1895000</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>2063000</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>2662000</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>2181000</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>2251000</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>2902000</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>2660000</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>1938000</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>1137000</v>
       </c>
-      <c r="R44" s="3"/>
-    </row>
-    <row r="45" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S44" s="3"/>
+    </row>
+    <row r="45" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>20794000</v>
+      </c>
+      <c r="E45" s="3">
         <v>17523000</v>
       </c>
-      <c r="E45" s="3">
-        <v>15521000</v>
-      </c>
       <c r="F45" s="3">
+        <v>15533000</v>
+      </c>
+      <c r="G45" s="3">
         <v>12613000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>10832000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>13471000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>11517000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>10133000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>6855000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>5203000</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>5965000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>7620000</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>6577000</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>5267000</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>5127000</v>
       </c>
-      <c r="R45" s="3"/>
-    </row>
-    <row r="46" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S45" s="3"/>
+    </row>
+    <row r="46" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>207710000</v>
+      </c>
+      <c r="E46" s="3">
         <v>191131000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>159734000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>184257000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>169684000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>184406000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>181915000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>175552000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>169662000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>162696000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>139660000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>122797000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>114246000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>101466000</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>85084000</v>
       </c>
-      <c r="R46" s="3"/>
-    </row>
-    <row r="47" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S46" s="3"/>
+    </row>
+    <row r="47" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>15405000</v>
+        <v>36348000</v>
       </c>
       <c r="E47" s="3">
+        <v>15133000</v>
+      </c>
+      <c r="F47" s="3">
         <v>14600000</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>9879000</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>6891000</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>5984000</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>2965000</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>2649000</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>1862000</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>7656000</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>10413000</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>12028000</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>14590000</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>10844000</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>9776000</v>
       </c>
-      <c r="R47" s="3"/>
-    </row>
-    <row r="48" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S47" s="3"/>
+    </row>
+    <row r="48" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>337253000</v>
+      </c>
+      <c r="E48" s="3">
         <v>229789000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>154552000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>109987000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>87546000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>70803000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>52904000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>43856000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>36146000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>78202000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>18356000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>14731000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>13011000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>9991000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>8269000</v>
       </c>
-      <c r="R48" s="3"/>
-    </row>
-    <row r="49" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S48" s="3"/>
+    </row>
+    <row r="49" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>138260000</v>
+      </c>
+      <c r="E49" s="3">
         <v>142113000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>146817000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>77252000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>78822000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>57511000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>50389000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>49776000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>43736000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>45228000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>21605000</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>21774000</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>27108000</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>17738000</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>16622000</v>
       </c>
-      <c r="R49" s="3"/>
-    </row>
-    <row r="50" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S49" s="3"/>
+    </row>
+    <row r="50" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2552,9 +2666,12 @@
       <c r="Q50" s="3">
         <v>0</v>
       </c>
-      <c r="R50" s="3"/>
-    </row>
-    <row r="51" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R50" s="3">
+        <v>0</v>
+      </c>
+      <c r="S50" s="3"/>
+    </row>
+    <row r="51" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2600,57 +2717,63 @@
       <c r="Q51" s="3">
         <v>0</v>
       </c>
-      <c r="R51" s="3"/>
-    </row>
-    <row r="52" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R51" s="3">
+        <v>0</v>
+      </c>
+      <c r="S51" s="3"/>
+    </row>
+    <row r="52" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>6257000</v>
+        <v>18191000</v>
       </c>
       <c r="E52" s="3">
+        <v>6529000</v>
+      </c>
+      <c r="F52" s="3">
         <v>9290000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>5938000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>4582000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>4494000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>4033000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>4987000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>4273000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>4443000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>3434000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>3142000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>3429000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>2392000</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>1520000</v>
       </c>
-      <c r="R52" s="3"/>
-    </row>
-    <row r="53" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S52" s="3"/>
+    </row>
+    <row r="53" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2696,57 +2819,63 @@
       <c r="Q53" s="3">
         <v>0</v>
       </c>
-      <c r="R53" s="3"/>
-    </row>
-    <row r="54" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R53" s="3">
+        <v>0</v>
+      </c>
+      <c r="S53" s="3"/>
+    </row>
+    <row r="54" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>758376000</v>
+      </c>
+      <c r="E54" s="3">
         <v>619003000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>512163000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>411976000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>364840000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>333779000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>301311000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>286556000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>258848000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>250312000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>193468000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>174472000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>172384000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>142431000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>121271000</v>
       </c>
-      <c r="R54" s="3"/>
-    </row>
-    <row r="55" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S54" s="3"/>
+    </row>
+    <row r="55" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2765,8 +2894,9 @@
       <c r="P55" s="3"/>
       <c r="Q55" s="3"/>
       <c r="R55" s="3"/>
-    </row>
-    <row r="56" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S55" s="3"/>
+    </row>
+    <row r="56" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2785,296 +2915,315 @@
       <c r="P56" s="3"/>
       <c r="Q56" s="3"/>
       <c r="R56" s="3"/>
-    </row>
-    <row r="57" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S56" s="3"/>
+    </row>
+    <row r="57" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>42416000</v>
+      </c>
+      <c r="E57" s="3">
         <v>27724000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>21996000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>18095000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>19000000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>15163000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>12530000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>9382000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>8617000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>7390000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>6898000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>6591000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>7432000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>4828000</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>4175000</v>
       </c>
-      <c r="R57" s="3"/>
-    </row>
-    <row r="58" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S57" s="3"/>
+    </row>
+    <row r="58" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>18910000</v>
+      </c>
+      <c r="E58" s="3">
         <v>11595000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>14871000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>8853000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>6037000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>10825000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>5905000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>7348000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>5573000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>10234000</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>12929000</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>7484000</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>2000000</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>2999000</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>1231000</v>
       </c>
-      <c r="R58" s="3"/>
-    </row>
-    <row r="59" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S58" s="3"/>
+    </row>
+    <row r="59" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>92554000</v>
+      </c>
+      <c r="E59" s="3">
         <v>88190000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>75855000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>66192000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>59384000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>52612000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>46001000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>45860000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>38195000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>38218000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>39530000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>35783000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>36193000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>29590000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>27282000</v>
       </c>
-      <c r="R59" s="3"/>
-    </row>
-    <row r="60" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S59" s="3"/>
+    </row>
+    <row r="60" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>168825000</v>
+      </c>
+      <c r="E60" s="3">
         <v>141218000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>125286000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>104149000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>95082000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>88657000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>72310000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>69420000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>58488000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>55745000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>59357000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>49647000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>45625000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>37417000</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>32688000</v>
       </c>
-      <c r="R60" s="3"/>
-    </row>
-    <row r="61" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S60" s="3"/>
+    </row>
+    <row r="61" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>109903000</v>
+      </c>
+      <c r="E61" s="3">
         <v>100589000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>82981000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>70588000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>72363000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>71453000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>76205000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>79107000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>81935000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>78498000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>41318000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>27808000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>20645000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>12601000</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>10713000</v>
       </c>
-      <c r="R61" s="3"/>
-    </row>
-    <row r="62" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S61" s="3"/>
+    </row>
+    <row r="62" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>31460000</v>
+      </c>
+      <c r="E62" s="3">
         <v>28172000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>30199000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>27671000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>27753000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>28867000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>31108000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>30936000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>31351000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>28358000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>34436000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>16934000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>16330000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>13469000</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>11507000</v>
       </c>
-      <c r="R62" s="3"/>
-    </row>
-    <row r="63" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S62" s="3"/>
+    </row>
+    <row r="63" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3120,9 +3269,12 @@
       <c r="Q63" s="3">
         <v>0</v>
       </c>
-      <c r="R63" s="3"/>
-    </row>
-    <row r="64" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R63" s="3">
+        <v>0</v>
+      </c>
+      <c r="S63" s="3"/>
+    </row>
+    <row r="64" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>19</v>
       </c>
@@ -3168,9 +3320,12 @@
       <c r="Q64" s="3">
         <v>0</v>
       </c>
-      <c r="R64" s="3"/>
-    </row>
-    <row r="65" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R64" s="3">
+        <v>0</v>
+      </c>
+      <c r="S64" s="3"/>
+    </row>
+    <row r="65" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3216,57 +3371,63 @@
       <c r="Q65" s="3">
         <v>0</v>
       </c>
-      <c r="R65" s="3"/>
-    </row>
-    <row r="66" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R65" s="3">
+        <v>0</v>
+      </c>
+      <c r="S65" s="3"/>
+    </row>
+    <row r="66" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>315989000</v>
+      </c>
+      <c r="E66" s="3">
         <v>275524000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>243686000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>205753000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>198298000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>191791000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>183007000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>184226000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>176130000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>162601000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>121471000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>94389000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>82600000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>63487000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>54908000</v>
       </c>
-      <c r="R66" s="3"/>
-    </row>
-    <row r="67" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S66" s="3"/>
+    </row>
+    <row r="67" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3285,8 +3446,9 @@
       <c r="P67" s="3"/>
       <c r="Q67" s="3"/>
       <c r="R67" s="3"/>
-    </row>
-    <row r="68" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S67" s="3"/>
+    </row>
+    <row r="68" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3332,9 +3494,12 @@
       <c r="Q68" s="3">
         <v>0</v>
       </c>
-      <c r="R68" s="3"/>
-    </row>
-    <row r="69" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R68" s="3">
+        <v>0</v>
+      </c>
+      <c r="S68" s="3"/>
+    </row>
+    <row r="69" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3380,9 +3545,12 @@
       <c r="Q69" s="3">
         <v>0</v>
       </c>
-      <c r="R69" s="3"/>
-    </row>
-    <row r="70" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R69" s="3">
+        <v>0</v>
+      </c>
+      <c r="S69" s="3"/>
+    </row>
+    <row r="70" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3428,9 +3596,12 @@
       <c r="Q70" s="3">
         <v>0</v>
       </c>
-      <c r="R70" s="3"/>
-    </row>
-    <row r="71" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R70" s="3">
+        <v>0</v>
+      </c>
+      <c r="S70" s="3"/>
+    </row>
+    <row r="71" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3476,57 +3647,63 @@
       <c r="Q71" s="3">
         <v>0</v>
       </c>
-      <c r="R71" s="3"/>
-    </row>
-    <row r="72" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R71" s="3">
+        <v>0</v>
+      </c>
+      <c r="S71" s="3"/>
+    </row>
+    <row r="72" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>328265000</v>
+      </c>
+      <c r="E72" s="3">
         <v>237731000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>173144000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>118848000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>84281000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>57055000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>34566000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>24150000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>13682000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>17769000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>2282000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>9096000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>17710000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>9895000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-856000</v>
       </c>
-      <c r="R72" s="3"/>
-    </row>
-    <row r="73" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S72" s="3"/>
+    </row>
+    <row r="73" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3572,9 +3749,12 @@
       <c r="Q73" s="3">
         <v>0</v>
       </c>
-      <c r="R73" s="3"/>
-    </row>
-    <row r="74" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R73" s="3">
+        <v>0</v>
+      </c>
+      <c r="S73" s="3"/>
+    </row>
+    <row r="74" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3620,9 +3800,12 @@
       <c r="Q74" s="3">
         <v>0</v>
       </c>
-      <c r="R74" s="3"/>
-    </row>
-    <row r="75" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R74" s="3">
+        <v>0</v>
+      </c>
+      <c r="S74" s="3"/>
+    </row>
+    <row r="75" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3668,57 +3851,63 @@
       <c r="Q75" s="3">
         <v>0</v>
       </c>
-      <c r="R75" s="3"/>
-    </row>
-    <row r="76" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R75" s="3">
+        <v>0</v>
+      </c>
+      <c r="S75" s="3"/>
+    </row>
+    <row r="76" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>442387000</v>
+      </c>
+      <c r="E76" s="3">
         <v>343479000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>268477000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>206223000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>166542000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>141988000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>118304000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>102330000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>82718000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>87711000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>71997000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>80083000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>89784000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>78944000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>66363000</v>
       </c>
-      <c r="R76" s="3"/>
-    </row>
-    <row r="77" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S76" s="3"/>
+    </row>
+    <row r="77" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3764,110 +3953,119 @@
       <c r="Q77" s="3">
         <v>0</v>
       </c>
-      <c r="R77" s="3"/>
-    </row>
-    <row r="79" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R77" s="3">
+        <v>0</v>
+      </c>
+      <c r="S77" s="3"/>
+    </row>
+    <row r="79" spans="2:19" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E80" s="2">
         <v>45838</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45473</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45107</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44742</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44377</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44012</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>43646</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>43281</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>42916</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>42551</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>42185</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>41820</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>41455</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>41090</v>
       </c>
-      <c r="R80" s="2"/>
-    </row>
-    <row r="81" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S80" s="2"/>
+    </row>
+    <row r="81" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>133749000</v>
+      </c>
+      <c r="E81" s="3">
         <v>101832000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>88136000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>72361000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>72738000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>61271000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>44281000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>39240000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>16571000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>25489000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>20539000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>12193000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>22074000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>21863000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>16978000</v>
       </c>
-      <c r="R81" s="3"/>
-    </row>
-    <row r="82" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S81" s="3"/>
+    </row>
+    <row r="82" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3886,56 +4084,60 @@
       <c r="P82" s="3"/>
       <c r="Q82" s="3"/>
       <c r="R82" s="3"/>
-    </row>
-    <row r="83" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S82" s="3"/>
+    </row>
+    <row r="83" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>34300000</v>
+      </c>
+      <c r="E83" s="3">
         <v>22000000</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>15200000</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>11000000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>12600000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>9300000</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>10700000</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>9700000</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>7700000</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>8778000</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>6622000</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>5957000</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>5212000</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>3755000</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>2967000</v>
       </c>
-      <c r="R83" s="3"/>
-    </row>
-    <row r="84" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S83" s="3"/>
+    </row>
+    <row r="84" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3981,9 +4183,12 @@
       <c r="Q84" s="3">
         <v>0</v>
       </c>
-      <c r="R84" s="3"/>
-    </row>
-    <row r="85" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R84" s="3">
+        <v>0</v>
+      </c>
+      <c r="S84" s="3"/>
+    </row>
+    <row r="85" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -4029,9 +4234,12 @@
       <c r="Q85" s="3">
         <v>0</v>
       </c>
-      <c r="R85" s="3"/>
-    </row>
-    <row r="86" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R85" s="3">
+        <v>0</v>
+      </c>
+      <c r="S85" s="3"/>
+    </row>
+    <row r="86" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4077,9 +4285,12 @@
       <c r="Q86" s="3">
         <v>0</v>
       </c>
-      <c r="R86" s="3"/>
-    </row>
-    <row r="87" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R86" s="3">
+        <v>0</v>
+      </c>
+      <c r="S86" s="3"/>
+    </row>
+    <row r="87" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4125,9 +4336,12 @@
       <c r="Q87" s="3">
         <v>0</v>
       </c>
-      <c r="R87" s="3"/>
-    </row>
-    <row r="88" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R87" s="3">
+        <v>0</v>
+      </c>
+      <c r="S87" s="3"/>
+    </row>
+    <row r="88" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4173,57 +4387,63 @@
       <c r="Q88" s="3">
         <v>0</v>
       </c>
-      <c r="R88" s="3"/>
-    </row>
-    <row r="89" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R88" s="3">
+        <v>0</v>
+      </c>
+      <c r="S88" s="3"/>
+    </row>
+    <row r="89" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>182935000</v>
+      </c>
+      <c r="E89" s="3">
         <v>136162000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>118548000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>87582000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>89035000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>76740000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>60675000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>52185000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>43884000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>39507000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>33325000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>29080000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>32231000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>28833000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>31626000</v>
       </c>
-      <c r="R89" s="3"/>
-    </row>
-    <row r="90" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S89" s="3"/>
+    </row>
+    <row r="90" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4242,56 +4462,60 @@
       <c r="P90" s="3"/>
       <c r="Q90" s="3"/>
       <c r="R90" s="3"/>
-    </row>
-    <row r="91" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S90" s="3"/>
+    </row>
+    <row r="91" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-115948000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-64551000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-44477000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-28107000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-23886000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-20622000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-15441000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-13925000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-11632000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-8129000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-8343000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-5944000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-5485000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-4257000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-2305000</v>
       </c>
-      <c r="R91" s="3"/>
-    </row>
-    <row r="92" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S91" s="3"/>
+    </row>
+    <row r="92" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4337,9 +4561,12 @@
       <c r="Q92" s="3">
         <v>0</v>
       </c>
-      <c r="R92" s="3"/>
-    </row>
-    <row r="93" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R92" s="3">
+        <v>0</v>
+      </c>
+      <c r="S92" s="3"/>
+    </row>
+    <row r="93" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4385,57 +4612,63 @@
       <c r="Q93" s="3">
         <v>0</v>
       </c>
-      <c r="R93" s="3"/>
-    </row>
-    <row r="94" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R93" s="3">
+        <v>0</v>
+      </c>
+      <c r="S93" s="3"/>
+    </row>
+    <row r="94" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-139500000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-72599000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-96970000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-22680000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-30311000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-27577000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-12223000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-15773000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-6061000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-46781000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-23950000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-23001000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-18833000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-23811000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-24786000</v>
       </c>
-      <c r="R94" s="3"/>
-    </row>
-    <row r="95" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S94" s="3"/>
+    </row>
+    <row r="95" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4454,56 +4687,60 @@
       <c r="P95" s="3"/>
       <c r="Q95" s="3"/>
       <c r="R95" s="3"/>
-    </row>
-    <row r="96" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S95" s="3"/>
+    </row>
+    <row r="96" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>26445000</v>
+      </c>
+      <c r="E96" s="3">
         <v>24082000</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>21771000</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>19800000</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>18135000</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>16521000</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>15137000</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>13811000</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>12699000</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>-11845000</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>-11006000</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>-9882000</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>-8879000</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>-7455000</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="R96" s="3">
         <v>-6385000</v>
       </c>
-      <c r="R96" s="3"/>
-    </row>
-    <row r="97" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S96" s="3"/>
+    </row>
+    <row r="97" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4549,9 +4786,12 @@
       <c r="Q97" s="3">
         <v>0</v>
       </c>
-      <c r="R97" s="3"/>
-    </row>
-    <row r="98" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R97" s="3">
+        <v>0</v>
+      </c>
+      <c r="S97" s="3"/>
+    </row>
+    <row r="98" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4597,9 +4837,12 @@
       <c r="Q98" s="3">
         <v>0</v>
       </c>
-      <c r="R98" s="3"/>
-    </row>
-    <row r="99" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R98" s="3">
+        <v>0</v>
+      </c>
+      <c r="S98" s="3"/>
+    </row>
+    <row r="99" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4645,151 +4888,163 @@
       <c r="Q99" s="3">
         <v>0</v>
       </c>
-      <c r="R99" s="3"/>
-    </row>
-    <row r="100" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R99" s="3">
+        <v>0</v>
+      </c>
+      <c r="S99" s="3"/>
+    </row>
+    <row r="100" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-52546000</v>
+      </c>
+      <c r="E100" s="3">
         <v>-51699000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-37757000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-43935000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-58876000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-48486000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-46031000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-36887000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-33590000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>8408000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-8393000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-9080000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-8394000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-8148000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-9408000</v>
       </c>
-      <c r="R100" s="3"/>
-    </row>
-    <row r="101" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S100" s="3"/>
+    </row>
+    <row r="101" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-196000</v>
+      </c>
+      <c r="E101" s="3">
         <v>63000</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-210000</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-194000</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-141000</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-29000</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-201000</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-115000</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>50000</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>19000</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-67000</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-73000</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-139000</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>-8000</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>-104000</v>
       </c>
-      <c r="R101" s="3"/>
-    </row>
-    <row r="102" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S101" s="3"/>
+    </row>
+    <row r="102" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-9307000</v>
+      </c>
+      <c r="E102" s="3">
         <v>11927000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-16389000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>20773000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-293000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>648000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>2220000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-590000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>4283000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>1153000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>915000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-3074000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>4865000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-3134000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-2672000</v>
       </c>
-      <c r="R102" s="3"/>
+      <c r="S102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
